--- a/data/processed/base_cda.xlsx
+++ b/data/processed/base_cda.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V85"/>
+  <dimension ref="A1:AA85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,31 @@
           <t>i_USD_fdt_pond</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>encaje_mn</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>encaje_me</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>encaje_mn_efec</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>encaje_me_efec</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>tpm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -597,6 +622,11 @@
       <c r="V2" t="n">
         <v>1</v>
       </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -667,6 +697,11 @@
       <c r="V3" t="n">
         <v>1.3</v>
       </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -737,6 +772,11 @@
       <c r="V4" t="n">
         <v>1.14</v>
       </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -807,6 +847,11 @@
       <c r="V5" t="n">
         <v>1.64</v>
       </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -877,6 +922,11 @@
       <c r="V6" t="n">
         <v>1.7</v>
       </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -947,6 +997,11 @@
       <c r="V7" t="n">
         <v>1.73</v>
       </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1017,6 +1072,11 @@
       <c r="V8" t="n">
         <v>2.19</v>
       </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1087,6 +1147,11 @@
       <c r="V9" t="n">
         <v>2.8</v>
       </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1157,6 +1222,11 @@
       <c r="V10" t="n">
         <v>3.43</v>
       </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1227,6 +1297,11 @@
       <c r="V11" t="n">
         <v>3.02</v>
       </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1297,6 +1372,11 @@
       <c r="V12" t="n">
         <v>3.56</v>
       </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1359,6 +1439,11 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1429,6 +1514,11 @@
       <c r="V14" t="n">
         <v>4.27</v>
       </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1499,6 +1589,11 @@
       <c r="V15" t="n">
         <v>3.52</v>
       </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1569,6 +1664,11 @@
       <c r="V16" t="n">
         <v>4.9</v>
       </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1639,6 +1739,11 @@
       <c r="V17" t="n">
         <v>4.32</v>
       </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1709,6 +1814,11 @@
       <c r="V18" t="n">
         <v>4.51</v>
       </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1779,6 +1889,11 @@
       <c r="V19" t="n">
         <v>3.72</v>
       </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1849,6 +1964,11 @@
       <c r="V20" t="n">
         <v>4.92</v>
       </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1919,6 +2039,11 @@
       <c r="V21" t="n">
         <v>5.83</v>
       </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1989,6 +2114,11 @@
       <c r="V22" t="n">
         <v>5.36</v>
       </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2059,6 +2189,11 @@
       <c r="V23" t="n">
         <v>4.66</v>
       </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2129,6 +2264,11 @@
       <c r="V24" t="n">
         <v>5.26</v>
       </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2199,6 +2339,11 @@
       <c r="V25" t="n">
         <v>4.53</v>
       </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2269,6 +2414,11 @@
       <c r="V26" t="n">
         <v>5.14</v>
       </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2339,6 +2489,11 @@
       <c r="V27" t="n">
         <v>4.81</v>
       </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2409,6 +2564,11 @@
       <c r="V28" t="n">
         <v>4.44</v>
       </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2479,6 +2639,11 @@
       <c r="V29" t="n">
         <v>4.65</v>
       </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2549,6 +2714,11 @@
       <c r="V30" t="n">
         <v>5.566336593625789</v>
       </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2619,6 +2789,13 @@
       <c r="V31" t="n">
         <v>5.508945295174336</v>
       </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="n">
+        <v>8.25</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2689,6 +2866,13 @@
       <c r="V32" t="n">
         <v>5.652552471699954</v>
       </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="n">
+        <v>8.416666666666666</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2759,6 +2943,13 @@
       <c r="V33" t="n">
         <v>6.25070792602946</v>
       </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="n">
+        <v>7.916666666666667</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2829,6 +3020,13 @@
       <c r="V34" t="n">
         <v>6.448445830522097</v>
       </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2899,6 +3097,13 @@
       <c r="V35" t="n">
         <v>6.11525370967986</v>
       </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="n">
+        <v>6.333333333333333</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2969,6 +3174,13 @@
       <c r="V36" t="n">
         <v>6.463104479776916</v>
       </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="n">
+        <v>5.666666666666667</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3039,6 +3251,21 @@
       <c r="V37" t="n">
         <v>6.272898178845449</v>
       </c>
+      <c r="W37" t="n">
+        <v>18</v>
+      </c>
+      <c r="X37" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3109,6 +3336,21 @@
       <c r="V38" t="n">
         <v>5.795416897680542</v>
       </c>
+      <c r="W38" t="n">
+        <v>18</v>
+      </c>
+      <c r="X38" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3179,6 +3421,21 @@
       <c r="V39" t="n">
         <v>6.520682623641008</v>
       </c>
+      <c r="W39" t="n">
+        <v>18</v>
+      </c>
+      <c r="X39" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3249,6 +3506,21 @@
       <c r="V40" t="n">
         <v>6.023584066422214</v>
       </c>
+      <c r="W40" t="n">
+        <v>18</v>
+      </c>
+      <c r="X40" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3319,6 +3591,21 @@
       <c r="V41" t="n">
         <v>5.448521801050124</v>
       </c>
+      <c r="W41" t="n">
+        <v>18</v>
+      </c>
+      <c r="X41" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>5.666666666666667</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3389,6 +3676,21 @@
       <c r="V42" t="n">
         <v>5.368390426369868</v>
       </c>
+      <c r="W42" t="n">
+        <v>18</v>
+      </c>
+      <c r="X42" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>6.666666666666667</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3459,6 +3761,21 @@
       <c r="V43" t="n">
         <v>4.640530963238413</v>
       </c>
+      <c r="W43" t="n">
+        <v>18</v>
+      </c>
+      <c r="X43" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>6.75</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3529,6 +3846,21 @@
       <c r="V44" t="n">
         <v>4.859631819080824</v>
       </c>
+      <c r="W44" t="n">
+        <v>18</v>
+      </c>
+      <c r="X44" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>6.75</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3599,6 +3931,21 @@
       <c r="V45" t="n">
         <v>4.614877409456064</v>
       </c>
+      <c r="W45" t="n">
+        <v>18</v>
+      </c>
+      <c r="X45" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>6.75</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3669,6 +4016,21 @@
       <c r="V46" t="n">
         <v>4.610716448814236</v>
       </c>
+      <c r="W46" t="n">
+        <v>18</v>
+      </c>
+      <c r="X46" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>6.666666666666667</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3739,6 +4101,21 @@
       <c r="V47" t="n">
         <v>4.882545293150212</v>
       </c>
+      <c r="W47" t="n">
+        <v>18</v>
+      </c>
+      <c r="X47" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>6.166666666666667</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3809,6 +4186,21 @@
       <c r="V48" t="n">
         <v>4.848184356215346</v>
       </c>
+      <c r="W48" t="n">
+        <v>18</v>
+      </c>
+      <c r="X48" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>5.75</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3879,6 +4271,21 @@
       <c r="V49" t="n">
         <v>4.941930697638047</v>
       </c>
+      <c r="W49" t="n">
+        <v>18</v>
+      </c>
+      <c r="X49" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>5.75</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3949,6 +4356,21 @@
       <c r="V50" t="n">
         <v>4.469377070141155</v>
       </c>
+      <c r="W50" t="n">
+        <v>18</v>
+      </c>
+      <c r="X50" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4019,6 +4441,21 @@
       <c r="V51" t="n">
         <v>4.842913323347396</v>
       </c>
+      <c r="W51" t="n">
+        <v>18</v>
+      </c>
+      <c r="X51" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>5.833333333333333</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4089,6 +4526,21 @@
       <c r="V52" t="n">
         <v>4.066768101256977</v>
       </c>
+      <c r="W52" t="n">
+        <v>18</v>
+      </c>
+      <c r="X52" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4159,6 +4611,21 @@
       <c r="V53" t="n">
         <v>3.971318781271818</v>
       </c>
+      <c r="W53" t="n">
+        <v>18</v>
+      </c>
+      <c r="X53" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4229,6 +4696,21 @@
       <c r="V54" t="n">
         <v>4.222587341471799</v>
       </c>
+      <c r="W54" t="n">
+        <v>18</v>
+      </c>
+      <c r="X54" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4299,6 +4781,21 @@
       <c r="V55" t="n">
         <v>4.239245759439672</v>
       </c>
+      <c r="W55" t="n">
+        <v>18</v>
+      </c>
+      <c r="X55" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4369,6 +4866,21 @@
       <c r="V56" t="n">
         <v>5.217310591712196</v>
       </c>
+      <c r="W56" t="n">
+        <v>18</v>
+      </c>
+      <c r="X56" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>5.333333333333333</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4439,6 +4951,21 @@
       <c r="V57" t="n">
         <v>4.076627066356401</v>
       </c>
+      <c r="W57" t="n">
+        <v>18</v>
+      </c>
+      <c r="X57" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>5.25</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4509,6 +5036,21 @@
       <c r="V58" t="n">
         <v>4.117279155136794</v>
       </c>
+      <c r="W58" t="n">
+        <v>18</v>
+      </c>
+      <c r="X58" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>5.25</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4579,6 +5121,21 @@
       <c r="V59" t="n">
         <v>4.460793481507349</v>
       </c>
+      <c r="W59" t="n">
+        <v>18</v>
+      </c>
+      <c r="X59" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>5.25</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4649,6 +5206,21 @@
       <c r="V60" t="n">
         <v>4.623862376924779</v>
       </c>
+      <c r="W60" t="n">
+        <v>18</v>
+      </c>
+      <c r="X60" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>5.25</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4719,6 +5291,21 @@
       <c r="V61" t="n">
         <v>4.435711214841189</v>
       </c>
+      <c r="W61" t="n">
+        <v>18</v>
+      </c>
+      <c r="X61" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>5.25</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4789,6 +5376,21 @@
       <c r="V62" t="n">
         <v>4.806775660524765</v>
       </c>
+      <c r="W62" t="n">
+        <v>18</v>
+      </c>
+      <c r="X62" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4859,6 +5461,21 @@
       <c r="V63" t="n">
         <v>4.979518810423087</v>
       </c>
+      <c r="W63" t="n">
+        <v>18</v>
+      </c>
+      <c r="X63" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>4.75</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4929,6 +5546,21 @@
       <c r="V64" t="n">
         <v>4.343501025377131</v>
       </c>
+      <c r="W64" t="n">
+        <v>18</v>
+      </c>
+      <c r="X64" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4999,6 +5631,21 @@
       <c r="V65" t="n">
         <v>3.961594914104609</v>
       </c>
+      <c r="W65" t="n">
+        <v>18</v>
+      </c>
+      <c r="X65" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5069,6 +5716,21 @@
       <c r="V66" t="n">
         <v>4.328540435416027</v>
       </c>
+      <c r="W66" t="n">
+        <v>18</v>
+      </c>
+      <c r="X66" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>3.416666666666667</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5139,6 +5801,21 @@
       <c r="V67" t="n">
         <v>4.42934132209414</v>
       </c>
+      <c r="W67" t="n">
+        <v>18</v>
+      </c>
+      <c r="X67" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>1.083333333333333</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5209,6 +5886,21 @@
       <c r="V68" t="n">
         <v>4.106839632897654</v>
       </c>
+      <c r="W68" t="n">
+        <v>18</v>
+      </c>
+      <c r="X68" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5279,6 +5971,21 @@
       <c r="V69" t="n">
         <v>3.507745980208677</v>
       </c>
+      <c r="W69" t="n">
+        <v>18</v>
+      </c>
+      <c r="X69" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5349,6 +6056,21 @@
       <c r="V70" t="n">
         <v>3.607573968980178</v>
       </c>
+      <c r="W70" t="n">
+        <v>18</v>
+      </c>
+      <c r="X70" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5419,6 +6141,21 @@
       <c r="V71" t="n">
         <v>2.675393545408113</v>
       </c>
+      <c r="W71" t="n">
+        <v>18</v>
+      </c>
+      <c r="X71" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5489,6 +6226,21 @@
       <c r="V72" t="n">
         <v>2.64120710674869</v>
       </c>
+      <c r="W72" t="n">
+        <v>18</v>
+      </c>
+      <c r="X72" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>1.083333333333333</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5559,6 +6311,21 @@
       <c r="V73" t="n">
         <v>2.922460589219344</v>
       </c>
+      <c r="W73" t="n">
+        <v>18</v>
+      </c>
+      <c r="X73" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5629,6 +6396,21 @@
       <c r="V74" t="n">
         <v>3.049638038860366</v>
       </c>
+      <c r="W74" t="n">
+        <v>18</v>
+      </c>
+      <c r="X74" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>5.833333333333333</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5699,6 +6481,21 @@
       <c r="V75" t="n">
         <v>3.855827069346909</v>
       </c>
+      <c r="W75" t="n">
+        <v>18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>7.25</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5769,6 +6566,21 @@
       <c r="V76" t="n">
         <v>4.282868183621811</v>
       </c>
+      <c r="W76" t="n">
+        <v>18</v>
+      </c>
+      <c r="X76" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>8.25</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5839,6 +6651,21 @@
       <c r="V77" t="n">
         <v>5.711872708875573</v>
       </c>
+      <c r="W77" t="n">
+        <v>18</v>
+      </c>
+      <c r="X77" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5909,6 +6736,21 @@
       <c r="V78" t="n">
         <v>5.630902683036125</v>
       </c>
+      <c r="W78" t="n">
+        <v>18</v>
+      </c>
+      <c r="X78" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5979,6 +6821,21 @@
       <c r="V79" t="n">
         <v>5.387398502348518</v>
       </c>
+      <c r="W79" t="n">
+        <v>18</v>
+      </c>
+      <c r="X79" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6049,6 +6906,21 @@
       <c r="V80" t="n">
         <v>5.658742174676749</v>
       </c>
+      <c r="W80" t="n">
+        <v>18</v>
+      </c>
+      <c r="X80" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>8.25</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6119,6 +6991,21 @@
       <c r="V81" t="n">
         <v>5.933744703924318</v>
       </c>
+      <c r="W81" t="n">
+        <v>18</v>
+      </c>
+      <c r="X81" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>7.25</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6189,6 +7076,21 @@
       <c r="V82" t="n">
         <v>5.898676837744674</v>
       </c>
+      <c r="W82" t="n">
+        <v>18</v>
+      </c>
+      <c r="X82" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6259,6 +7161,21 @@
       <c r="V83" t="n">
         <v>5.839100333380423</v>
       </c>
+      <c r="W83" t="n">
+        <v>18</v>
+      </c>
+      <c r="X83" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6329,6 +7246,21 @@
       <c r="V84" t="n">
         <v>5.9</v>
       </c>
+      <c r="W84" t="n">
+        <v>18</v>
+      </c>
+      <c r="X84" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6398,6 +7330,21 @@
       </c>
       <c r="V85" t="n">
         <v>5.74</v>
+      </c>
+      <c r="W85" t="n">
+        <v>18</v>
+      </c>
+      <c r="X85" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/base_cda.xlsx
+++ b/data/processed/base_cda.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fuentes_trazabilidad" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7350,4 +7352,1198 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>unidad</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>regla_agregacion</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Año calendario</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>trimestre</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Trimestre (1-4)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Etiqueta YYYYQn</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>i_Gs</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tasa efectiva CDA &lt;=365 días, bancos, moneda nacional (SERIE PRIMARIA)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>% anual</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BCP-SB, boletines 'Promedio de Tasas'</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>promedio de meses publicados del trimestre</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>84/84 (10 meses no publicados, ver fuentes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>i_USD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tasa efectiva CDA &lt;=365 días, bancos, moneda extranjera (SERIE PRIMARIA)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>% anual</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BCP-SB, 'Promedio de Tasas'</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>promedio de meses publicados</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>i_Gs_fdt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CDA &lt;=365 Gs, último mes publicado del trimestre</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>% anual</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BCP-SB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>último mes publicado</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>i_USD_fdt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CDA &lt;=365 USD, último mes publicado</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>% anual</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BCP-SB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>último mes publicado</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>meses_cobertura</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cantidad de meses publicados usados en el promedio del trimestre</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BCP-SB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>conteo</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ultimo_mes_publicado</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mes del dato fdt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1-12</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BCP-SB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tipo de cambio nominal Gs/USD, promedio del último mes del trimestre</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gs/USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BCP, Anexo Estadístico, Cuadro 60a col E</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>valor del mes de cierre</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dolariz</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Participación de depósitos en moneda extranjera</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>% del total</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BCP, Anexo Estadístico, Cuadro 23a col O</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>valor del mes de cierre</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IPC_PY</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IPC Paraguay, nivel (dic-2017=100)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>índice</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BCP, Anexo Estadístico, Cuadro 15 col V</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>valor del mes de cierre</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>infl_PY_yoy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Inflación interanual Paraguay (publicada)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BCP, Cuadro 15 col Y</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>valor del mes de cierre</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IPC_US</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CPI EEUU (CPIAUCSL), nivel</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>índice</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>valor del mes de cierre</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>infl_US_yoy</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inflación interanual EEUU</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>derivada de CPIAUCSL: (CPI_t/CPI_t-12 -1)x100</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>mes de cierre</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FEDFUNDS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Federal Funds Effective Rate</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>% anual</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>promedio de los 3 meses</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>i_Gs_vista</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tasa a la vista MN (referencia, NO CDA)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>% anual</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BCP, Cuadro 31 col C</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>promedio 3 meses</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>i_USD_vista</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tasa a la vista ME (referencia, NO CDA)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>% anual</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BCP, Cuadro 31 Cont. col C</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>promedio 3 meses</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>84/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>i_Gs_pond</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CDA promedio ponderado MN (SENSIBILIDAD; empalme 2010/2011)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>% anual</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BCP: IF mensuales 2004-2010 + Cuadro 31 2011+</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>promedio 3 meses</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>83/84 (falta 2006Q4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>i_USD_pond</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CDA promedio ponderado ME (SENSIBILIDAD)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>% anual</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ídem</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>promedio 3 meses</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>83/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>i_Gs_fdt_pond</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ponderada MN, fin de trimestre</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>% anual</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ídem</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>último mes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>83/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>i_USD_fdt_pond</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ponderada ME, fin de trimestre</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>% anual</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ídem</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>último mes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>83/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>encaje_mn</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tasa de encaje legal MN, tramo &lt;=360 días (base)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Resoluciones BCP (docs/11_encaje_fuentes.md)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>vigente al cierre</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>49/84 (verificado 2012Q4+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>encaje_me</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tasa de encaje legal ME, tramo &lt;=360 días (base)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Resoluciones BCP</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vigente al cierre</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>49/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>encaje_mn_efec</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Encaje MN efectivo (incluye desencaje COVID 2020)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Resoluciones BCP</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>vigente al cierre</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>49/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>encaje_me_efec</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Encaje ME efectivo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Resoluciones BCP</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>vigente al cierre</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>49/84</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>tpm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tasa de Política Monetaria</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>% anual</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BCP, TPM.xlsx oficial (data/raw/bcp/TPM.xlsx)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>promedio de meses del trimestre</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>55/84 (la TPM nace en may-2011; pre-2011 no existe, no es hueco)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fuente_oficial_exacta</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>url_y_archivo_crudo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>reglas_y_notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>i_Gs / i_USD (y fdt)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BCP - Superintendencia de Bancos, boletines mensuales 'Promedio de Tasas', fila 'CERTIFIC. DEP. DE AHORRO' tramo '&lt;=365 dias', tasa efectiva, Bancos</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.bcp.gov.py (Promedio de Tasas; 242 boletines descargados en data/raw/bcp/promedio_tasas/full/)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fuente única 2004-2024, sin empalme. 10 meses NO publicados por el BCP: 2005-07, 2006-03, 2006-11, 2006-12, 2007-01, 2007-05, 2007-07, 2013-04, 2013-05, 2014-04. Trimestre=promedio de meses publicados (meses_cobertura).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BCP - Anexo Estadístico del Informe Económico, Cuadro 60a, col E</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.bcp.gov.py/anexo-estadistico-del-informe-economico-i365 (archivo en data/raw/bcp/Anexo_Estadistico_Informe_Economico.xlsx)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Promedio mensual del mes de cierre del trimestre (la cotización diaria de cierre no existe homogénea 2004-2024).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dolariz</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BCP - Anexo Estadístico, Cuadro 23a, col O (depósitos sector privado, participación ME)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ídem Anexo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mes de cierre. 2024Q2-Q4 marcados preliminares por la fuente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IPC_PY / infl_PY_yoy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BCP - Anexo Estadístico, Cuadro 15, cols V (índice) e Y (interanual publicada)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ídem Anexo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mes de cierre; la inflación es la publicada por el BCP, no recalculada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>IPC_US / infl_US_yoy</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FRED, serie CPIAUCSL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=CPIAUCSL (data/raw/fred/CPIAUCSL.csv)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Nivel del mes de cierre; interanual derivada (CPI_t/CPI_t-12 -1)x100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FEDFUNDS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FRED, serie FEDFUNDS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=FEDFUNDS (data/raw/fred/FEDFUNDS.csv)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Promedio de los 3 meses del trimestre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>i_*_pond</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BCP: Informes de Indicadores Financieros mensuales 2004-2010 (PDF, data/raw/bcp/if_pdfs/ + _INVENTARIO.csv con URL por archivo) empalmados con Cuadro 31 del Anexo 2011-2024</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ver _INVENTARIO.csv y Anexo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SOLO SENSIBILIDAD: empalme 2010/2011 (~0,7-0,8pp definicional) y composición de plazos variable. Hueco: 2006Q4 (PDF escaneado ilegible).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>encaje_*</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Resoluciones del BCP (Res. 30/2012 MN 18%, Res. 31/2012 ME 24%, tramo &lt;=360d; desencaje COVID 2020: MN 7 / ME 15)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>detalle y enlaces en docs/11_encaje_fuentes.md</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cobertura verificada 2012Q4-2024Q4; 2004-2012Q3 vacío (resoluciones escaneadas pendientes de OCR). Salvedad de tramo: encaje corta en 360d, CDA en 365d.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tpm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BCP - Tasa de Política Monetaria, archivo oficial TPM.xlsx (serie mensual desde may-2011)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.bcp.gov.py/web/institucional/tasa-de-politica-monetaria (data/raw/bcp/TPM.xlsx; mensual intermedio en data/processed/tpm_mensual.csv)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Trimestre = promedio de meses disponibles (2011Q2 = may+jun). Pre-2011: la TPM no existía (no es dato faltante).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>